--- a/finance/output/Luxury_Goods_Companies_Financial_Metrics_20250506_163746.xlsx
+++ b/finance/output/Luxury_Goods_Companies_Financial_Metrics_20250506_163746.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\finance_script\finance\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A29AC72A-CF3D-4684-8EE3-93DC92A4F65E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D21AF22-6E19-4EB1-9553-50E7DB7009A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -582,12 +582,14 @@
   <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="10" max="10" width="16.06640625" customWidth="1"/>
+    <col min="8" max="8" width="20.265625" customWidth="1"/>
+    <col min="9" max="9" width="16.796875" customWidth="1"/>
+    <col min="10" max="10" width="21.6640625" customWidth="1"/>
     <col min="11" max="11" width="19.59765625" customWidth="1"/>
     <col min="12" max="12" width="14.9296875" customWidth="1"/>
     <col min="13" max="13" width="25.46484375" customWidth="1"/>
-    <col min="14" max="14" width="24.46484375" customWidth="1"/>
-    <col min="15" max="15" width="22.46484375" customWidth="1"/>
+    <col min="14" max="14" width="32.46484375" customWidth="1"/>
+    <col min="15" max="15" width="28.86328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
